--- a/Empirical_analysis/stock_prices_motifs/motifs_analysis.xlsx
+++ b/Empirical_analysis/stock_prices_motifs/motifs_analysis.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,35 +383,35 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D2">
-        <v>15.03029668155857</v>
+        <v>2.531410751016161</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>6.417429406230733</v>
+        <v>1.416230500664643</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -421,54 +421,54 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D4">
-        <v>10.07579427543388</v>
+        <v>2.272588418884844</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>14.49707536369915</v>
+        <v>2.693442757818411</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>70</v>
+        <v>244</v>
       </c>
       <c r="D6">
-        <v>10.76374375161405</v>
+        <v>14.27293120384753</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -478,35 +478,35 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>7.453386937676875</v>
+        <v>0.9335931358507077</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B8">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>7.612066579277109</v>
+        <v>0.9899239533960761</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -516,39 +516,39 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>7.676317814025945</v>
+        <v>3.159085931608854</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D10">
-        <v>6.525917665148065</v>
+        <v>3.538243048824397</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
@@ -557,13 +557,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>11.17913478691381</v>
+        <v>1.562540524545196</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -573,54 +573,54 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C12">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>11.74252716519412</v>
+        <v>2.076715233998967</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>6.175563690092463</v>
+        <v>2.325013691374738</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B14">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D14">
-        <v>8.929911469865502</v>
+        <v>4.706259833829475</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -630,73 +630,73 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B15">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C15">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D15">
-        <v>10.63374589553802</v>
+        <v>3.883481878469457</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>7.528250603485073</v>
+        <v>2.138426691214249</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17">
-        <v>10.79582994132508</v>
+        <v>3.034245060566983</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>random</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D18">
-        <v>3.680584578447973</v>
+        <v>2.742940131220875</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -706,16 +706,16 @@
     </row>
     <row r="19">
       <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19">
+        <v>26</v>
+      </c>
+      <c r="C19">
         <v>24</v>
       </c>
-      <c r="B19">
-        <v>50</v>
-      </c>
-      <c r="C19">
-        <v>13</v>
-      </c>
       <c r="D19">
-        <v>8.128559865071782</v>
+        <v>2.207306564557242</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -725,16 +725,16 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B20">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D20">
-        <v>17.15813381458733</v>
+        <v>4.61972346342713</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -744,16 +744,16 @@
     </row>
     <row r="21">
       <c r="A21">
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>28</v>
+      </c>
+      <c r="C21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>53</v>
-      </c>
-      <c r="C21">
-        <v>49</v>
-      </c>
       <c r="D21">
-        <v>18.7776805093679</v>
+        <v>3.987601376470901</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -763,16 +763,16 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B22">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C22">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D22">
-        <v>14.60483469007571</v>
+        <v>4.205045999162595</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>580</v>
       </c>
       <c r="D23">
-        <v>13.47697213562774</v>
+        <v>16.54962180499094</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B24">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>211</v>
       </c>
       <c r="D24">
-        <v>9.917032245219012</v>
+        <v>16.71054025653818</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -820,16 +820,16 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B25">
+        <v>31</v>
+      </c>
+      <c r="C25">
         <v>56</v>
       </c>
-      <c r="C25">
-        <v>11</v>
-      </c>
       <c r="D25">
-        <v>10.1017658537903</v>
+        <v>5.025579502411156</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -839,16 +839,16 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B26">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>9.634452896547485</v>
+        <v>1.869522709149554</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B27">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D27">
-        <v>3.994591813494113</v>
+        <v>3.91619994793624</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -877,16 +877,16 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B28">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C28">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D28">
-        <v>13.88179355804556</v>
+        <v>5.816787544486613</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D29">
-        <v>25.03850498306425</v>
+        <v>2.251383327154766</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -918,13 +918,13 @@
         <v>37</v>
       </c>
       <c r="B30">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C30">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>15.26769831008071</v>
+        <v>3.271969734328981</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B31">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D31">
-        <v>13.36970639318548</v>
+        <v>9.990734802023473</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -953,16 +953,16 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B32">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C32">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D32">
-        <v>21.5137394765671</v>
+        <v>2.815070578726595</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C33">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D33">
-        <v>14.48487340011446</v>
+        <v>5.898227048648734</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -991,16 +991,16 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B34">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D34">
-        <v>11.74252716519412</v>
+        <v>4.456406606096989</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1010,16 +1010,16 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B35">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D35">
-        <v>10.92938092790552</v>
+        <v>6.358781907094815</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C36">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D36">
-        <v>27.86536842778575</v>
+        <v>4.082676413526112</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B37">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D37">
-        <v>28.04866604174738</v>
+        <v>4.637377157585963</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1067,16 +1067,16 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C38">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D38">
-        <v>22.53192694336046</v>
+        <v>8.587445524848242</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1086,16 +1086,16 @@
     </row>
     <row r="39">
       <c r="A39">
+        <v>57</v>
+      </c>
+      <c r="B39">
         <v>40</v>
       </c>
-      <c r="B39">
-        <v>87</v>
-      </c>
       <c r="C39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>10.63374589553802</v>
+        <v>6.417429406230733</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1105,37 +1105,550 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D40">
-        <v>40.71779253837134</v>
+        <v>16.02231525369289</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B41">
+        <v>41</v>
+      </c>
+      <c r="C41">
+        <v>52</v>
+      </c>
+      <c r="D41">
+        <v>10.3271684516585</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>14</v>
+      </c>
+      <c r="B42">
+        <v>42</v>
+      </c>
+      <c r="C42">
+        <v>70</v>
+      </c>
+      <c r="D42">
+        <v>10.76374375161405</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>60</v>
+      </c>
+      <c r="B43">
+        <v>44</v>
+      </c>
+      <c r="C43">
+        <v>10</v>
+      </c>
+      <c r="D43">
+        <v>7.453386937676875</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>49</v>
+      </c>
+      <c r="B44">
+        <v>45</v>
+      </c>
+      <c r="C44">
+        <v>22</v>
+      </c>
+      <c r="D44">
+        <v>7.612066579277109</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>50</v>
+      </c>
+      <c r="B45">
+        <v>45</v>
+      </c>
+      <c r="C45">
+        <v>23</v>
+      </c>
+      <c r="D45">
+        <v>7.676317814025945</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>53</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46">
+        <v>25</v>
+      </c>
+      <c r="D46">
+        <v>9.042670425711057</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>22</v>
+      </c>
+      <c r="B47">
+        <v>47</v>
+      </c>
+      <c r="C47">
+        <v>37</v>
+      </c>
+      <c r="D47">
+        <v>5.025579502411156</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>36</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>28</v>
+      </c>
+      <c r="D48">
+        <v>5.695662457922153</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>27</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49">
+        <v>55</v>
+      </c>
+      <c r="D49">
+        <v>10.66277370473022</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>41</v>
+      </c>
+      <c r="B50">
+        <v>48</v>
+      </c>
+      <c r="C50">
+        <v>28</v>
+      </c>
+      <c r="D50">
+        <v>7.257315017830258</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>67</v>
+      </c>
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>10.79582994132508</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>46</v>
+      </c>
+      <c r="B52">
+        <v>50</v>
+      </c>
+      <c r="C52">
+        <v>40</v>
+      </c>
+      <c r="D52">
+        <v>16.66757744204714</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>54</v>
+      </c>
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>3.680584578447973</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <v>50</v>
+      </c>
+      <c r="C54">
+        <v>23</v>
+      </c>
+      <c r="D54">
+        <v>14.27293120384753</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>42</v>
+      </c>
+      <c r="B55">
+        <v>54</v>
+      </c>
+      <c r="C55">
+        <v>39</v>
+      </c>
+      <c r="D55">
+        <v>9.494422698875644</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>58</v>
+      </c>
+      <c r="B56">
+        <v>56</v>
+      </c>
+      <c r="C56">
+        <v>12</v>
+      </c>
+      <c r="D56">
+        <v>8.812572099036249</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>63</v>
+      </c>
+      <c r="B57">
+        <v>56</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
+      <c r="D57">
+        <v>9.529914627054628</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>45</v>
+      </c>
+      <c r="B58">
+        <v>58</v>
+      </c>
+      <c r="C58">
+        <v>44</v>
+      </c>
+      <c r="D58">
+        <v>15.3078923024291</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>28</v>
+      </c>
+      <c r="B59">
+        <v>59</v>
+      </c>
+      <c r="C59">
+        <v>78</v>
+      </c>
+      <c r="D59">
+        <v>16.54962180499094</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>52</v>
+      </c>
+      <c r="B60">
+        <v>60</v>
+      </c>
+      <c r="C60">
+        <v>40</v>
+      </c>
+      <c r="D60">
+        <v>25.03850498306425</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>62</v>
+      </c>
+      <c r="B61">
+        <v>62</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>9.516941709484389</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>64</v>
+      </c>
+      <c r="B62">
+        <v>62</v>
+      </c>
+      <c r="C62">
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <v>13.36970639318548</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>59</v>
+      </c>
+      <c r="B63">
+        <v>63</v>
+      </c>
+      <c r="C63">
+        <v>28</v>
+      </c>
+      <c r="D63">
+        <v>21.67237737401201</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>65</v>
+      </c>
+      <c r="B64">
+        <v>68</v>
+      </c>
+      <c r="C64">
+        <v>12</v>
+      </c>
+      <c r="D64">
+        <v>10.92938092790552</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65">
+        <v>69</v>
+      </c>
+      <c r="C65">
+        <v>14</v>
+      </c>
+      <c r="D65">
+        <v>16.71054025653818</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>56</v>
+      </c>
+      <c r="B66">
+        <v>74</v>
+      </c>
+      <c r="C66">
+        <v>35</v>
+      </c>
+      <c r="D66">
+        <v>29.98788243950183</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>48</v>
+      </c>
+      <c r="B67">
+        <v>80</v>
+      </c>
+      <c r="C67">
+        <v>47</v>
+      </c>
+      <c r="D67">
+        <v>22.53192694336046</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>51</v>
+      </c>
+      <c r="B68">
         <v>150</v>
       </c>
-      <c r="C41">
-        <v>37</v>
-      </c>
-      <c r="D41">
-        <v>47.76107432606066</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="C68">
+        <v>43</v>
+      </c>
+      <c r="D68">
+        <v>40.71779253837134</v>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>random</t>
         </is>
